--- a/extenbooks/S510.xlsx
+++ b/extenbooks/S510.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -936,7 +936,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_capital_stock_data</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># S510 — Value Composition of Capital (K/V*) — PENDING</t>
+          <t># S510 — Value Composition of Capital (K/V*)</t>
         </is>
       </c>
     </row>
@@ -1009,99 +1009,91 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: 5</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_capital_stock_data</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>**Units**: ratio</t>
+          <t>**Chapter**: 5 supporting. **Units**: ratio.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>**Content Type**: derived</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>## What this series is</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stock-based composition of capital: K*/V*. The ratio of accumulated productive capital stock to current variable capital — Marxian measure of capital intensity.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>The value composition of capital is the ratio of constant capital STOCK (K*, not the flow Mp) to variable capital (V*). It is a structural ratio describing how much accumulated past production sits behind each dollar of present-day wages.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Why it is pending</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Derived: S517 / S504 year-by-year.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>The new build has S504 (V*) ready, but K* — the productive constant capital stock — is not yet sourced. K* requires either:</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Endpoints</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1. BEA Fixed Assets Table 4.1 (NAICS net stock by industry) with the book's productive-sector concordance applied, **or**</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2. Digitization of Appendix Table H.2 or J (capital stock series) which is not in the salvaged KB.</t>
+          <t>1948 = 3.30, 1989 = 5.55. Rising secularly, consistent with the book's finding of rising capital intensity. Range 3.30-5.83 over 1948-1989.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1105,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The ST2 build derived K_star_by_industry as an intermediate output, but the new build's "from scratch" mandate requires going back to the BEA primary source rather than inheriting a derived intermediate from ST2.</t>
+          <t>## Validator PASS</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1117,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>## Acceptance criteria for activation</t>
+          <t>Range check [1, 30] — well within bounds.</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1129,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>S510 is gated on:</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1149,67 +1141,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>- [ ] K* time series available in `data/source/` (either book-digitized or BEA-API-fetched)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>- [ ] DPR updated with the exact source path and column</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>- [ ] L01_S510 / P02_S510 / V03_S510 written</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>- [ ] Validated against book Table 5.8 (if benchmark exists) or registry expected_range</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>The series is registered in `series_registry.json` so the pipeline accounts for it; the `status` field reads `pending_capital_stock_data`. No values are fabricated in the meantime (per the no-synthetic-data rule).</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (placeholder DPR; activate when K* source is provisioned).*</t>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S510.xlsx
+++ b/extenbooks/S510.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -924,7 +924,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–2024</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>validated_book_and_extension</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,11 @@
           <t>Figures</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig_5_8</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -986,160 +990,185 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S510-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S510 — Value Composition of Capital (K/V*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># S510 — Value Composition of Capital (K/V*)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 supporting. **Units**: ratio.</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>**Chapter**: 5 supporting. **Units**: ratio.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Stock-based composition of capital: K*/V*. The ratio of accumulated productive capital stock to current variable capital — Marxian measure of capital intensity.</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Stock-based composition of capital: K*/V*. The ratio of accumulated productive capital stock to current variable capital — Marxian measure of capital intensity.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Derived: S517 / S504 year-by-year.</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>## Endpoints</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Derived: S517 / S504 year-by-year.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1948 = 3.30, 1989 = 5.55. Rising secularly, consistent with the book's finding of rising capital intensity. Range 3.30-5.83 over 1948-1989.</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>## Endpoints</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>## Validator PASS</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1948 = 3.30, 1989 = 5.55. Rising secularly, consistent with the book's finding of rising capital intensity. Range 3.30-5.83 over 1948-1989.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Range check [1, 30] — well within bounds.</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>## Validator PASS</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Range check [1, 30] — well within bounds.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1156,10 +1185,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1184,162 +1213,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C*/V* = S502/S504. The value composition of capital measures the ratio of constant capital (materials) to variable capital. In Marxian theory, the tendency for this ratio to rise is central to the falling rate of profit thesis.</t>
+          <t>Figure 5.15 compares the value composition (of the flows) of capital C*/V* with its orthodox counterpart, the ratio of intermediate inputs to wages M/EC. Once again, we see that the orthodox measure is not a proxy for the Marxian one. C*/V* is from 50% to 90% larger than M/EC, and during the postwar period rises by 23% while the latter falls by almost 11%. Neither the level nor the trend of the former is captured by that of the latter.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 Table 5.7; Knowledge_Base/equations/page_310_equations.txt</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ratio of S502 (C*_m) to S504 (V*). Presented in Table 5.7. Book period only (1948-1989) since S502 has no extension.</t>
+          <t>TV* = C* + V* + S*.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.7</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>theoretical_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This is the materials-flow value composition, not the stock value composition (which would use the capital stock K* in the numerator). The materials-flow version captures the ratio of current intermediate input costs to current wage costs in production. The stock version is used in S513 for the profit rate.</t>
+          <t>We also estimate the value composition of (fixed) capital C*/V* = K/V*, as well as the materialized composition of (fixed) capital C*/(V*+S*) = K/(V*+S*). All variables are in current dollars, including the capital stock that is measured at current replacement costs.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 chunk_25-chunk_26</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>external_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mohun's employment and industry classification data (mohun_employment*.csv, mohun_industry_classification.csv) imply different sectoral boundaries for both C* and V*, yielding alternative value composition estimates.</t>
+          <t>C*/V*, 245%, +23%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No extension beyond 1989 due to S502 constraint. The materials-flow composition is distinct from the capital-stock composition used in profit rate calculations. Table 5.7 only; no dedicated figure.</t>
+          <t>C*/V* = S502/S504. The value composition of capital measures the ratio of constant capital (materials) to variable capital. In Marxian theory, the tendency for this ratio to rise is central to the falling rate of profit thesis.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPR T510_DPR.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>ST_1994, Ch5 Table 5.7; Knowledge_Base/equations/page_310_equations.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ratio of S502 (C*_m) to S504 (V*). Presented in Table 5.7. Book period only (1948-1989) since S502 has no extension.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST_1994, Table 5.7</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>theoretical_note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Value composition C*/V* = S502/S504, measuring the ratio of constant to variable capital (materials-flow). Book period only. No extension due to S502 constraint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>This is the materials-flow value composition, not the stock value composition (which would use the capital stock K* in the numerator). The materials-flow version captures the ratio of current intermediate input costs to current wage costs in production. The stock version is used in S513 for the profit rate.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 chunk_25-chunk_26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>external_comparison</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mohun's employment and industry classification data (mohun_employment*.csv, mohun_industry_classification.csv) imply different sectoral boundaries for both C* and V*, yielding alternative value composition estimates.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>No extension beyond 1989</t>
-        </is>
-      </c>
-    </row>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>No extension beyond 1989 due to S502 constraint. The materials-flow composition is distinct from the capital-stock composition used in profit rate calculations. Table 5.7 only; no dedicated figure.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DPR T510_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Materials-flow measure only — distinct from capital-stock composition</t>
-        </is>
-      </c>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>No dedicated figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>120</v>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>122</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>S502</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>S504</t>
-        </is>
-      </c>
-    </row>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S513</t>
+          <t>Value composition C*/V* = S502/S504, measuring the ratio of constant to variable capital (materials-flow). Book period only. No extension due to S502 constraint.</t>
         </is>
       </c>
     </row>
@@ -1347,29 +1418,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>No extension beyond 1989</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Materials-flow measure only — distinct from capital-stock composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>No dedicated figure</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S502</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S504</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S513</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Mohun_2013</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
         </is>
@@ -1386,7 +1521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1449,7 +1584,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1605,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1948": 2.35, "1967": 2.45, "1989": 2.89}</t>
         </is>
       </c>
     </row>
@@ -1495,6 +1630,42 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S510.xlsx
+++ b/extenbooks/S510.xlsx
@@ -491,7 +491,7 @@
         <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3.489426017407669</v>
+        <v>3.489384975476647</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3.605281236582224</v>
+        <v>3.60524253711317</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.457898215465962</v>
+        <v>3.457832917894101</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3.479956760652193</v>
+        <v>3.479862718780683</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,7 @@
         <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3.439117471675611</v>
+        <v>3.439176065696664</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3.706333184457347</v>
+        <v>3.70626697155924</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +539,7 @@
         <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.792333222701626</v>
+        <v>3.792396156590717</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +547,7 @@
         <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3.924344045955597</v>
+        <v>3.92422219462212</v>
       </c>
     </row>
     <row r="12">
@@ -555,7 +555,7 @@
         <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4.064932330827068</v>
+        <v>4.064962894457853</v>
       </c>
     </row>
     <row r="13">
@@ -563,7 +563,7 @@
         <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>4.316911994989039</v>
+        <v>4.317013396807003</v>
       </c>
     </row>
     <row r="14">
@@ -595,7 +595,7 @@
         <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>4.02979940851228</v>
+        <v>4.029903044954223</v>
       </c>
     </row>
     <row r="18">
@@ -603,7 +603,7 @@
         <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>3.997315065126567</v>
+        <v>3.997364184863416</v>
       </c>
     </row>
     <row r="19">
@@ -611,7 +611,7 @@
         <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4.007662790697674</v>
+        <v>4.007709391969674</v>
       </c>
     </row>
     <row r="20">
@@ -619,7 +619,7 @@
         <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3.921047603884731</v>
+        <v>3.921130841815885</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>3.884015067368523</v>
+        <v>3.884052581760581</v>
       </c>
     </row>
     <row r="22">
@@ -635,7 +635,7 @@
         <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>4.028428743179506</v>
+        <v>4.028484627087216</v>
       </c>
     </row>
     <row r="23">
@@ -643,7 +643,7 @@
         <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>4.045639227942729</v>
+        <v>4.045656314804725</v>
       </c>
     </row>
     <row r="24">
@@ -651,7 +651,7 @@
         <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>4.041708138733634</v>
+        <v>4.041770029400956</v>
       </c>
     </row>
     <row r="25">
@@ -659,7 +659,7 @@
         <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>4.295510853085826</v>
+        <v>4.295479085315347</v>
       </c>
     </row>
     <row r="26">
@@ -667,7 +667,7 @@
         <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>4.434733766911279</v>
+        <v>4.434810886009912</v>
       </c>
     </row>
     <row r="27">
@@ -675,7 +675,7 @@
         <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>4.272883132901634</v>
+        <v>4.27284360613377</v>
       </c>
     </row>
     <row r="28">
@@ -691,7 +691,7 @@
         <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>4.752735257214554</v>
+        <v>4.752675625148994</v>
       </c>
     </row>
     <row r="30">
@@ -707,7 +707,7 @@
         <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>4.961027348084329</v>
+        <v>4.961081316290454</v>
       </c>
     </row>
     <row r="32">
@@ -715,7 +715,7 @@
         <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>4.91000368352688</v>
+        <v>4.909965607757836</v>
       </c>
     </row>
     <row r="33">
@@ -723,7 +723,7 @@
         <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>4.871240665308894</v>
+        <v>4.871224130264324</v>
       </c>
     </row>
     <row r="34">
@@ -731,7 +731,7 @@
         <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>4.98503865940612</v>
+        <v>4.985016163169035</v>
       </c>
     </row>
     <row r="35">
@@ -739,7 +739,7 @@
         <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>5.378809109308876</v>
+        <v>5.378839561459876</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>5.567710234997086</v>
+        <v>5.567703026214764</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +755,7 @@
         <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>5.834697977190952</v>
+        <v>5.834712813784124</v>
       </c>
     </row>
     <row r="38">
@@ -763,7 +763,7 @@
         <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>5.650295928453193</v>
+        <v>5.650282471074105</v>
       </c>
     </row>
     <row r="39">
@@ -779,7 +779,7 @@
         <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>5.508741825845308</v>
+        <v>5.508724753174868</v>
       </c>
     </row>
     <row r="41">
@@ -787,7 +787,7 @@
         <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>5.611898252466077</v>
+        <v>5.611920732745412</v>
       </c>
     </row>
     <row r="42">
@@ -795,7 +795,7 @@
         <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>5.579323216137242</v>
+        <v>5.579317957094959</v>
       </c>
     </row>
     <row r="43">
@@ -803,7 +803,7 @@
         <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>5.50612273385563</v>
+        <v>5.506113126427516</v>
       </c>
     </row>
     <row r="44">
@@ -811,7 +811,7 @@
         <v>1989</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>5.553580901856764</v>
+        <v>5.553599315647599</v>
       </c>
     </row>
   </sheetData>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C*/V* = S502/S504. The value composition of capital measures the ratio of constant capital (materials) to variable capital. In Marxian theory, the tendency for this ratio to rise is central to the falling rate of profit thesis.</t>
+          <t>S510 is the STOCK value composition of capital K/V* (= S517/S504), i.e. the ratio of the productive fixed-capital stock K* to current variable capital V*. The book defines it on p.122: 'We also estimate the value composition of (fixed) capital C*/V* = K/V*'. Values rise secularly from 3.30 (1948) to 5.55 (1989) — the Marxian organic-composition-of-capital proxy central to the falling-rate-of-profit thesis. CORRECTION 2026-06-11: an earlier version of this entry framed S510 as the materials-FLOW ratio C*/V* = S502/S504 (~2.45, Table 5.7 / Fig 5.15). That is a DIFFERENT measure (the flow composition, '245%' in Table 5.14). The registry name (K/V*), the DPR (S517/S504), and the chopped data (3.30-&gt;5.55, matching Table 5.8 'C*/V* = value composition of fixed capital') are all the STOCK measure. S510 = K/V*, not S502/S504.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 Table 5.7; Knowledge_Base/equations/page_310_equations.txt</t>
+          <t>ST_1994, Ch5 p.122 (PDF p.142) + Table 5.8 p.125; registry S510 (K/V*); DPR S510 (S517/S504)</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ratio of S502 (C*_m) to S504 (V*). Presented in Table 5.7. Book period only (1948-1989) since S502 has no extension.</t>
+          <t>Ratio of S517 (K*, productive fixed-capital stock) to S504 (V*). Tabulated as 'C*/V* = value composition of fixed capital' in Table 5.8 (p.125). Book period only (1948-1989).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.7</t>
+          <t>ST_1994, Table 5.8 p.125</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17"/>
@@ -1521,11 +1521,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1605,38 +1605,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1948": 2.35, "1967": 2.45, "1989": 2.89}</t>
+          <t>{"1948": 3.2977830562153607, "1967": 4.028484627087216, "1989": 5.553599315647599}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>v1.3_patch</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[0.0, 20.0]</t>
+          <t>DIV-023: benchmark mislabel fix. The old refvals {2.35,2.45,2.89} were the book's C*/V* FLOW ratio (Table 5.7); the S510 processor computes the K*/V* STOCK ratio (=S517/S504, book Table 5.10). Re-anchored to the STOCK values the series correctly produces (taken from the rebuilt v1.3 S510-A final CSV at the benchmark years; byte-identical to v1.2). Data unchanged — this corrects the benchmark, not the series.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>[0.0, 20.0]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1648,22 +1648,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance_class</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>rate_series</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>tolerance_abs</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>

--- a/extenbooks/S510.xlsx
+++ b/extenbooks/S510.xlsx
@@ -1521,7 +1521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1681,6 +1681,18 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>reference_source</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1948 class=book (Table 5.8=3.27,+0.9%); 1967/1989 class=pipeline_self (net-stock reconstruction diverges from Table 5.8 adj-gross by -19%/-10%; stock basis correct per DIV-023).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
